--- a/AAA - Revision Asignacion de Salida (version Abril Julio 2026-caculado el 2026-03-05).xlsx
+++ b/AAA - Revision Asignacion de Salida (version Abril Julio 2026-caculado el 2026-03-05).xlsx
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
         <v>7.218153325542461</v>
@@ -1465,13 +1465,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5024793388429751</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="R16" t="n">
-        <v>2.763636363636363</v>
+        <v>2.985714285714285</v>
       </c>
       <c r="S16" t="n">
-        <v>0.837465564738292</v>
+        <v>0.9047619047619048</v>
       </c>
     </row>
   </sheetData>
